--- a/boards_missing.xlsx
+++ b/boards_missing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(재)한국우편사업진흥원</t>
+          <t>(재)일제강제동원피해자지원재단</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.posa.or.kr/</t>
+          <t>https://www.fomo.or.kr/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(재)한국통계정보원</t>
+          <t>(재)축산환경관리원</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.kosii.or.kr/</t>
+          <t>https://www.lemi.or.kr/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -601,7 +601,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑</t>
+          <t>(재)한국우편사업진흥원</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.gongyoung.kr/</t>
+          <t>https://www.posa.or.kr/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -621,27 +621,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(주)한국가스기술공사</t>
+          <t>(재)한국통계정보원</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.kogas-tech.or.kr/</t>
+          <t>https://www.kosii.or.kr/</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -651,17 +651,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 403</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>가축위생방역지원본부</t>
+          <t>(주)공영홈쇼핑</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.lhca.or.kr/</t>
+          <t>https://www.gongyoung.kr/</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -691,17 +691,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>건강보험심사평가원</t>
+          <t>(주)한국가스기술공사</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.hira.or.kr/</t>
+          <t>https://www.kogas-tech.or.kr/</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: 403</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>경상국립대학교병원</t>
+          <t>88관광개발(주)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>http://www.gnuh.co.kr/</t>
+          <t>https://www.88countryclub.co.kr/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -751,7 +751,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>공간정보산업진흥원</t>
+          <t>가축위생방역지원본부</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.spacen.or.kr/</t>
+          <t>https://www.lhca.or.kr/</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -771,17 +771,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>과학기술사업화진흥원</t>
+          <t>강원대학교병원</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.compa.re.kr/</t>
+          <t>https://www.knuh.or.kr/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -811,17 +811,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>과학기술정책연구원</t>
+          <t>건강보험심사평가원</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.stepi.re.kr/</t>
+          <t>https://www.hira.or.kr/</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -841,17 +841,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>국립공원공단</t>
+          <t>경북대학교치과병원</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.knps.or.kr/</t>
+          <t>https://www.knudh.kr/</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -861,17 +861,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국립광주과학관</t>
+          <t>경상국립대학교병원</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.sciencecenter.or.kr/</t>
+          <t>http://www.gnuh.co.kr/</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -891,17 +891,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>국립농업박물관</t>
+          <t>공간정보산업진흥원</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://namuk.or.kr/</t>
+          <t>https://www.spacen.or.kr/</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -921,17 +921,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>국립대구과학관</t>
+          <t>공간정보품질관리원</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.dnsm.or.kr/</t>
+          <t>https://www.siqms.or.kr/</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>국립박물관문화재단</t>
+          <t>공무원연금공단</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.nmf.or.kr/</t>
+          <t>https://www.geps.or.kr/</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>국립부산과학관</t>
+          <t>과학기술사업화진흥원</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>http://www.sciport.or.kr/</t>
+          <t>https://www.compa.re.kr/</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1021,17 +1021,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>국립생태원</t>
+          <t>과학기술정책연구원</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>http://www.nie.re.kr/</t>
+          <t>https://www.stepi.re.kr/</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>국립아시아문화전당재단</t>
+          <t>국가수리과학연구소</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.accf.or.kr/</t>
+          <t>http://www.nims.re.kr/</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>국립울진해양과학관</t>
+          <t>국가아동권리보장원</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.kosm.or.kr/</t>
+          <t>https://www.ncrc.or.kr/</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1101,27 +1101,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>국립인천해양박물관</t>
+          <t>국립공원공단</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.inmm.or.kr/</t>
+          <t>https://www.knps.or.kr/</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1131,17 +1131,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>국립중앙의료원</t>
+          <t>국립광주과학관</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.nmc.or.kr/</t>
+          <t>https://www.sciencecenter.or.kr/</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>국립항공박물관</t>
+          <t>국립낙동강생물자원관</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://wwww.aviation.or.kr/</t>
+          <t>https://www.nnibr.re.kr/</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1201,17 +1201,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>국민건강보험공단</t>
+          <t>국립농업박물관</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.nhis.or.kr/</t>
+          <t>https://namuk.or.kr/</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>국방과학연구소</t>
+          <t>국립대구과학관</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.add.re.kr/</t>
+          <t>https://www.dnsm.or.kr/</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>국방기술진흥연구소</t>
+          <t>국립박물관문화재단</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.krit.re.kr/</t>
+          <t>https://www.nmf.or.kr/</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>국방전직교육원</t>
+          <t>국립부산과학관</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.moti.or.kr/</t>
+          <t>http://www.sciport.or.kr/</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1311,27 +1311,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 400</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>국악방송</t>
+          <t>국립생태원</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.igbf.kr/</t>
+          <t>http://www.nie.re.kr/</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1341,17 +1341,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>국립아시아문화전당재단</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.arirang.com/</t>
+          <t>https://www.accf.or.kr/</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>국토교통과학기술진흥원</t>
+          <t>국립울진해양과학관</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.kaia.re.kr/</t>
+          <t>https://www.kosm.or.kr/</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1411,17 +1411,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>국토안전관리원</t>
+          <t>국립항공박물관</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>http://www.kalis.or.kr/</t>
+          <t>https://wwww.aviation.or.kr/</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>그랜드코리아레저(주)</t>
+          <t>국립호남권생물자원관</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.grandkorea.com/</t>
+          <t>http://hnibr.re.kr/</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1461,27 +1461,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>근로복지공단</t>
+          <t>국민건강보험공단</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.comwel.or.kr/</t>
+          <t>https://www.nhis.or.kr/</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 400</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1501,7 +1501,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>농림수산식품교육문화정보원</t>
+          <t>국방과학연구소</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.epis.or.kr/</t>
+          <t>https://www.add.re.kr/</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>대외경제정책연구원</t>
+          <t>국방기술진흥연구소</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.kiep.go.kr/</t>
+          <t>https://www.krit.re.kr/</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,7 +1561,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>대한장애인체육회</t>
+          <t>국방전직교육원</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>http://www.koreanpc.kr/</t>
+          <t>https://www.moti.or.kr/</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: 400</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>동남권원자력의학원</t>
+          <t>국악방송</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.dirams.re.kr/</t>
+          <t>https://www.igbf.kr/</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1611,17 +1611,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>민주화운동기념사업회</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.kdemo.or.kr/</t>
+          <t>https://www.arirang.com/</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>부산대학교치과병원</t>
+          <t>국토교통과학기술진흥원</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.pnudh.co.kr/</t>
+          <t>https://www.kaia.re.kr/</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1671,27 +1671,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>북한이탈주민지원재단</t>
+          <t>국토안전관리원</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.koreahana.or.kr/</t>
+          <t>http://www.kalis.or.kr/</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1711,17 +1711,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>그랜드코리아레저(주)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.tp.or.kr/</t>
+          <t>https://www.grandkorea.com/</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1731,27 +1731,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
+          <t>근로복지공단</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>http://snuh.org/</t>
+          <t>https://www.comwel.or.kr/</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1761,27 +1761,27 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: 400</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>서울대학교치과병원</t>
+          <t>기술보증기금</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>http://www.snudh.org/</t>
+          <t>https://www.kibo.or.kr/</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1791,27 +1791,27 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>소상공인시장진흥공단</t>
+          <t>농림수산식품교육문화정보원</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.semas.or.kr/</t>
+          <t>https://www.epis.or.kr/</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1821,27 +1821,27 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>수도권매립지관리공사</t>
+          <t>대한무역투자진흥공사</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>http://www.slc.or.kr/</t>
+          <t>http://www.kotra.or.kr/</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1861,7 +1861,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>시청자미디어재단</t>
+          <t>대한석탄공사</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.kcmf.or.kr/</t>
+          <t>https://www.kocoal.or.kr/</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>신용보증기금</t>
+          <t>대한장애인체육회</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>http://www.kodit.co.kr/</t>
+          <t>http://www.koreanpc.kr/</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1911,17 +1911,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>신용보증재단중앙회</t>
+          <t>대한체육회</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>http://www.koreg.or.kr/</t>
+          <t>https://www.sports.or.kr/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1951,7 +1951,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>여수광양항만공사</t>
+          <t>독립기념관</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.ygpa.or.kr/</t>
+          <t>https://www.i815.or.kr/</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1981,7 +1981,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>영상물등급위원회</t>
+          <t>동남권원자력의학원</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.kmrb.or.kr/</t>
+          <t>https://www.dirams.re.kr/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>영화진흥위원회</t>
+          <t>민주화운동기념사업회</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.kofic.or.kr/</t>
+          <t>https://www.kdemo.or.kr/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2031,17 +2031,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>육아정책연구소</t>
+          <t>부산대학교병원</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.kicce.re.kr/</t>
+          <t>http://www.pnuh.or.kr/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>재단법인 건설기술교육원</t>
+          <t>부산대학교치과병원</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.kicte.or.kr/</t>
+          <t>https://www.pnudh.co.kr/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2091,17 +2091,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>재단법인 대한건설기계안전관리원</t>
+          <t>북한이탈주민지원재단</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.kcesi.or.kr/</t>
+          <t>https://www.koreahana.or.kr/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2121,17 +2121,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>재외동포협력센터</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.okocc.or.kr/</t>
+          <t>https://www.tp.or.kr/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 403</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>전국재해구호협회</t>
+          <t>서민금융진흥원</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://hopebridge.or.kr/</t>
+          <t>https://www.kinfa.or.kr/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2181,27 +2181,27 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>정보통신기획평가원</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>http://www.iitp.kr/</t>
+          <t>http://snuh.org/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2221,7 +2221,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>정보통신정책연구원</t>
+          <t>선박해양플랜트연구소</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>http://www.kisdi.re.kr/</t>
+          <t>https://www.kriso.re.kr/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2241,27 +2241,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>정부법무공단</t>
+          <t>소상공인시장진흥공단</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>http://www.kgls.or.kr/</t>
+          <t>https://www.semas.or.kr/</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2271,27 +2271,27 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>제주국제자유도시개발센터</t>
+          <t>수도권매립지관리공사</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.jdcenter.com/</t>
+          <t>http://www.slc.or.kr/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2301,27 +2301,27 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>시청자미디어재단</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.khug.or.kr/</t>
+          <t>https://www.kcmf.or.kr/</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2331,27 +2331,27 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>중소벤처기업진흥공단</t>
+          <t>식품안전정보원</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.kosmes.or.kr/</t>
+          <t>http://www.foodinfo.or.kr/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2361,27 +2361,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>중앙사회서비스원</t>
+          <t>신용보증기금</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.kcpass.or.kr/</t>
+          <t>http://www.kodit.co.kr/</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>코레일네트웍스(주)</t>
+          <t>신용보증재단중앙회</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.korailnetworks.com/</t>
+          <t>http://www.koreg.or.kr/</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2421,17 +2421,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>코레일테크(주)</t>
+          <t>양육비이행관리원</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.korailtech.com/</t>
+          <t>https://www.childsupport.or.kr/</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2451,27 +2451,27 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>한국고용정보원</t>
+          <t>여수광양항만공사</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://keis.or.kr/</t>
+          <t>https://www.ygpa.or.kr/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2491,17 +2491,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>영상물등급위원회</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.koica.go.kr/</t>
+          <t>https://www.kmrb.or.kr/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2511,27 +2511,27 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>한국국토정보공사</t>
+          <t>영화진흥위원회</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.lx.or.kr/</t>
+          <t>https://www.kofic.or.kr/</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2541,17 +2541,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>한국나노기술원</t>
+          <t>오송첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.kanc.re.kr/</t>
+          <t>https://www.kbiohealth.kr/</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2581,17 +2581,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>한국남동발전(주)</t>
+          <t>육아정책연구소</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.koenergy.kr/</t>
+          <t>https://www.kicce.re.kr/</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2611,7 +2611,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>한국남부발전(주)</t>
+          <t>인천국제공항공사</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.kospo.co.kr/</t>
+          <t>https://www.airport.kr/</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2641,17 +2641,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>한국도로공사</t>
+          <t>재단법인 건설기술교육원</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.ex.co.kr/</t>
+          <t>https://www.kicte.or.kr/</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2661,27 +2661,27 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>한국도로교통공단</t>
+          <t>재단법인 대한건설기계안전관리원</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.koroad.or.kr/</t>
+          <t>https://www.kcesi.or.kr/</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>한국도박문제예방치유원</t>
+          <t>재단법인 한국에너지재단</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.kcgp.or.kr/</t>
+          <t>https://www.koref.or.kr/</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2721,27 +2721,27 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>한국동서발전(주)</t>
+          <t>재외동포협력센터</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.ewp.co.kr/</t>
+          <t>https://www.okocc.or.kr/</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 502</t>
+          <t>홈페이지 접속 실패: 403</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2761,7 +2761,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>한국마약퇴치운동본부</t>
+          <t>전국재해구호협회</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://drugfree.or.kr/</t>
+          <t>https://hopebridge.or.kr/</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2791,17 +2791,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>한국문화관광연구원</t>
+          <t>정보통신기획평가원</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>http://www.kcti.re.kr/</t>
+          <t>http://www.iitp.kr/</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2811,27 +2811,27 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>한국법무보호복지공단</t>
+          <t>정보통신정책연구원</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://koreha.or.kr/</t>
+          <t>http://www.kisdi.re.kr/</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2851,7 +2851,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>한국보건복지인재원</t>
+          <t>정부법무공단</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.kohi.or.kr/</t>
+          <t>http://www.kgls.or.kr/</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2871,27 +2871,27 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>한국보건의료연구원</t>
+          <t>제주국제자유도시개발센터</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.neca.re.kr/</t>
+          <t>https://www.jdcenter.com/</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2901,27 +2901,27 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>한국보건의료인국가시험원</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.kuksiwon.or.kr/</t>
+          <t>https://www.khug.or.kr/</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>한국사학진흥재단</t>
+          <t>중소벤처기업진흥공단</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.kasfo.or.kr/</t>
+          <t>https://www.kosmes.or.kr/</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2961,27 +2961,27 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>한국사회보장정보원</t>
+          <t>중앙사회서비스원</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>http://www.ssis.or.kr/</t>
+          <t>https://www.kcpass.or.kr/</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>한국사회복지협의회</t>
+          <t>충남대학교병원</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/</t>
+          <t>https://www.cnuh.co.kr/</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3021,27 +3021,27 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>한국산림복지진흥원</t>
+          <t>코레일네트웍스(주)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.fowi.or.kr/</t>
+          <t>https://www.korailnetworks.com/</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3061,7 +3061,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>한국산업기술시험원</t>
+          <t>코레일테크(주)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.ktl.re.kr/</t>
+          <t>https://www.korailtech.com/</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3091,17 +3091,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>한국산업단지공단</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.kicox.or.kr/</t>
+          <t>https://www.kogas.or.kr/</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한국산업안전보건공단</t>
+          <t>한국고용정보원</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://kosha.or.kr/</t>
+          <t>https://keis.or.kr/</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3141,17 +3141,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한국산업은행</t>
+          <t>한국과학창의재단</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>http://www.kdb.co.kr/</t>
+          <t>https://www.kosac.re.kr/</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3171,27 +3171,27 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한국서부발전(주)</t>
+          <t>한국광해광업공단</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.iwest.co.kr/</t>
+          <t>https://www.komir.or.kr/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3201,17 +3201,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한국소방산업기술원</t>
+          <t>한국교육개발원</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.kfi.or.kr/</t>
+          <t>https://www.kedi.re.kr/</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3231,27 +3231,27 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientResponseError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한국소비자원</t>
+          <t>한국교육과정평가원</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.kca.go.kr/</t>
+          <t>https://www.kice.re.kr/</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3261,17 +3261,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한국수출입은행</t>
+          <t>한국교육학술정보원</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.koreaexim.go.kr/</t>
+          <t>https://www.keris.or.kr/</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3291,27 +3291,27 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한국식품안전관리인증원</t>
+          <t>한국교통안전공단</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.haccp.or.kr/</t>
+          <t>https://www.kotsa.or.kr/</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3321,27 +3321,27 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한국어촌어항공단</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.fipa.or.kr/</t>
+          <t>https://www.koica.go.kr/</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3361,17 +3361,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한국여성인권진흥원</t>
+          <t>한국국토정보공사</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.stop.or.kr/</t>
+          <t>https://www.lx.or.kr/</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3391,7 +3391,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한국예술인복지재단</t>
+          <t>한국기상산업기술원</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>http://www.kawf.kr/</t>
+          <t>https://www.kmiti.or.kr/</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3411,27 +3411,27 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한국원자력환경공단</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.korad.or.kr/</t>
+          <t>https://www.koreatech.ac.kr/</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3451,7 +3451,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한국임업진흥원</t>
+          <t>한국나노기술원</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.kofpi.or.kr/</t>
+          <t>https://www.kanc.re.kr/</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3481,17 +3481,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
+          <t>한국남동발전(주)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>http://www.kamco.or.kr/</t>
+          <t>https://www.koenergy.kr/</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3501,27 +3501,27 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한국잡월드</t>
+          <t>한국남부발전(주)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>http://www.koreajobworld.or.kr/</t>
+          <t>https://www.kospo.co.kr/</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>한국재정정보원</t>
+          <t>한국농수산식품유통공사</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.fis.kr/</t>
+          <t>https://www.at.or.kr/</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3571,17 +3571,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한국전기안전공사</t>
+          <t>한국농업기술진흥원</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>http://www.kesco.or.kr/</t>
+          <t>https://www.koat.or.kr/</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3591,17 +3591,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
+          <t>한국도로공사</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://kepco.co.kr/</t>
+          <t>https://www.ex.co.kr/</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3631,17 +3631,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국조폐공사</t>
+          <t>한국도로공사서비스(주)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.komsco.com/</t>
+          <t>https://www.exservice.co.kr/</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3651,27 +3651,27 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국중부발전(주)</t>
+          <t>한국도로교통공단</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.komipo.co.kr/</t>
+          <t>https://www.koroad.or.kr/</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3681,17 +3681,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국중소벤처기업유통원</t>
+          <t>한국도박문제예방치유원</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.kodma.or.kr/</t>
+          <t>https://www.kcgp.or.kr/</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3711,27 +3711,27 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국지능정보사회진흥원</t>
+          <t>한국동서발전(주)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.nia.or.kr/</t>
+          <t>https://www.ewp.co.kr/</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국지식재산연구원</t>
+          <t>한국마약퇴치운동본부</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.kiip.re.kr/</t>
+          <t>https://drugfree.or.kr/</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3771,27 +3771,27 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국지역난방공사</t>
+          <t>한국문화관광연구원</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.kdhc.co.kr/</t>
+          <t>http://www.kcti.re.kr/</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3811,17 +3811,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국철도공사</t>
+          <t>한국물기술인증원</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://info.korail.com/</t>
+          <t>https://www.kwtc.or.kr/</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3831,27 +3831,27 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국청소년상담복지개발원</t>
+          <t>한국법무보호복지공단</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>http://www.kyci.or.kr/</t>
+          <t>https://koreha.or.kr/</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3861,17 +3861,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국출판문화산업진흥원</t>
+          <t>한국법제연구원</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>http://www.kpipa.or.kr/</t>
+          <t>https://www.klri.re.kr/</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국치산기술협회</t>
+          <t>한국벤처투자</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.kafet.or.kr/</t>
+          <t>https://www.kvic.or.kr/</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국특허정보원</t>
+          <t>한국보건복지인재원</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.kipi.or.kr/</t>
+          <t>https://www.kohi.or.kr/</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -3961,17 +3961,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국해양교통안전공단</t>
+          <t>한국보건의료연구원</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.komsa.or.kr/</t>
+          <t>https://www.neca.re.kr/</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3981,17 +3981,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국해양수산개발원</t>
+          <t>한국보건의료인국가시험원</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.kmi.re.kr/</t>
+          <t>https://www.kuksiwon.or.kr/</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4011,27 +4011,27 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국해양조사협회</t>
+          <t>한국부동산원</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.khra.kr/</t>
+          <t>https://www.reb.or.kr/</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국해외인프라도시개발지원공사</t>
+          <t>한국사학진흥재단</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.kindkorea.or.kr/</t>
+          <t>https://www.kasfo.or.kr/</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4071,27 +4071,27 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국행정연구원</t>
+          <t>한국사회보장정보원</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.kipa.re.kr/</t>
+          <t>http://www.ssis.or.kr/</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4101,17 +4101,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
+          <t>한국사회복지협의회</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.keci.or.kr/</t>
+          <t>https://www.bokji.net/</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>게시판 후보 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>해양수산과학기술진흥원</t>
+          <t>한국사회적기업진흥원</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.kimst.re.kr/</t>
+          <t>https://www.socialenterprise.or.kr/</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4161,40 +4161,1720 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>한국산림복지진흥원</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://www.fowi.or.kr/</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>한국산업기술시험원</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://www.ktl.re.kr/</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>한국산업기술진흥원</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://www.kiat.or.kr/</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>한국산업단지공단</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://www.kicox.or.kr/</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://kosha.or.kr/</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>한국산업은행</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>http://www.kdb.co.kr/</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>한국생명존중희망재단</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://www.kfsp.or.kr/</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>한국서부발전(주)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://www.iwest.co.kr/</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>한국석유관리원</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>http://www.kpetro.or.kr/</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>한국세라믹기술원</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://www.kicet.re.kr/</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 시간 초과</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>한국소방산업기술원</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://www.kfi.or.kr/</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 실패: ClientResponseError</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>한국소비자원</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://www.kca.go.kr/</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>한국수력원자력(주)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://www.khnp.co.kr/</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>한국수목원정원관리원</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://www.koagi.or.kr/</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>한국수자원공사</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://www.kwater.or.kr/</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>한국수출입은행</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://www.koreaexim.go.kr/</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>한국스포츠레저(주)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://www.kospole.co.kr/</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>한국식품산업클러스터진흥원</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://www.foodpolis.kr/</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>한국식품안전관리인증원</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://www.haccp.or.kr/</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>한국어촌어항공단</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://www.fipa.or.kr/</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>한국여성인권진흥원</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://www.stop.or.kr/</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>한국여성정책연구원</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://www.kwdi.re.kr/</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>한국원자력환경공단</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://www.korad.or.kr/</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>한국의약품안전관리원</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://www.drugsafe.or.kr/</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>한국임업진흥원</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://www.kofpi.or.kr/</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>한국자산관리공사</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>http://www.kamco.or.kr/</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>한국잡월드</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>http://www.koreajobworld.or.kr/</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>한국장애인개발원</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://www.koddi.or.kr/</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>한국장학재단</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://www.kosaf.go.kr/</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>한국재정정보원</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://www.fis.kr/</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 시간 초과</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>한국전기안전공사</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>http://www.kesco.or.kr/</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>한국전력공사</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://kepco.co.kr/</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 시간 초과</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>한국전력기술주식회사</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://www.kepco-enc.com/</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>한국조세재정연구원</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://www.kipf.re.kr/</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>한국조폐공사</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://www.komsco.com/</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>한국중부발전(주)</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://www.komipo.co.kr/</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://www.kodma.or.kr/</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>한국지능정보사회진흥원</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://www.nia.or.kr/</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>한국지식재산연구원</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://www.kiip.re.kr/</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>한국지역난방공사</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://www.kdhc.co.kr/</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 시간 초과</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>한국직업능력연구원</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://www.krivet.re.kr/</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>한국철도공사</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://info.korail.com/</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>한국청소년상담복지개발원</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>http://www.kyci.or.kr/</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 시간 초과</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>한국청소년활동진흥원</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://www.kywa.or.kr/</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 시간 초과</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>한국치산기술협회</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://www.kafet.or.kr/</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>한국투자공사</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>https://www.kic.kr/</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>한국특허정보원</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://www.kipi.or.kr/</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>한국항로표지기술원</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://www.katon.or.kr/</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>한국해양교통안전공단</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://www.komsa.or.kr/</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 시간 초과</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>한국해양수산개발원</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://www.kmi.re.kr/</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>한국해양조사협회</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://www.khra.kr/</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>한국해양진흥공사</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://www.kobc.or.kr/</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>한국환경보전원</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://www.keci.or.kr/</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>한전KPS(주)</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://www.kps.co.kr/</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>항공안전기술원</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://www.kiast.or.kr/</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>해양수산과학기술진흥원</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://www.kimst.re.kr/</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
           <t>해양환경공단</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>https://www.koem.or.kr/</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>게시판 후보 없음</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
         <v>1</v>
       </c>
     </row>

--- a/boards_missing.xlsx
+++ b/boards_missing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -601,7 +601,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>(재)한국우편사업진흥원</t>
+          <t>(재)한국통계정보원</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.posa.or.kr/</t>
+          <t>https://www.kosii.or.kr/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(재)한국통계정보원</t>
+          <t>(주)공영홈쇼핑</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.kosii.or.kr/</t>
+          <t>https://www.gongyoung.kr/</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -661,17 +661,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑</t>
+          <t>(주)한국가스기술공사</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.gongyoung.kr/</t>
+          <t>https://www.kogas-tech.or.kr/</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -681,27 +681,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: 403</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>(주)한국가스기술공사</t>
+          <t>88관광개발(주)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.kogas-tech.or.kr/</t>
+          <t>https://www.88countryclub.co.kr/</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 403</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>88관광개발(주)</t>
+          <t>가축위생방역지원본부</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.88countryclub.co.kr/</t>
+          <t>https://www.lhca.or.kr/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>가축위생방역지원본부</t>
+          <t>강원대학교병원</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.lhca.or.kr/</t>
+          <t>https://www.knuh.or.kr/</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -781,17 +781,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강원대학교병원</t>
+          <t>건강보험심사평가원</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.knuh.or.kr/</t>
+          <t>https://www.hira.or.kr/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -811,17 +811,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>건강보험심사평가원</t>
+          <t>경상국립대학교병원</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.hira.or.kr/</t>
+          <t>http://www.gnuh.co.kr/</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>경북대학교치과병원</t>
+          <t>공간정보산업진흥원</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.knudh.kr/</t>
+          <t>https://www.spacen.or.kr/</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -871,7 +871,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>경상국립대학교병원</t>
+          <t>공간정보품질관리원</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>http://www.gnuh.co.kr/</t>
+          <t>https://www.siqms.or.kr/</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -891,27 +891,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>공간정보산업진흥원</t>
+          <t>공무원연금공단</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.spacen.or.kr/</t>
+          <t>https://www.geps.or.kr/</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -931,7 +931,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>공간정보품질관리원</t>
+          <t>과학기술사업화진흥원</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.siqms.or.kr/</t>
+          <t>https://www.compa.re.kr/</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>공무원연금공단</t>
+          <t>과학기술정책연구원</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.geps.or.kr/</t>
+          <t>https://www.stepi.re.kr/</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>과학기술사업화진흥원</t>
+          <t>국가수리과학연구소</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.compa.re.kr/</t>
+          <t>http://www.nims.re.kr/</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>과학기술정책연구원</t>
+          <t>국가아동권리보장원</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.stepi.re.kr/</t>
+          <t>https://www.ncrc.or.kr/</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>국가수리과학연구소</t>
+          <t>국가철도공단</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>http://www.nims.re.kr/</t>
+          <t>https://www.kr.or.kr/</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1071,27 +1071,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>국가아동권리보장원</t>
+          <t>국립공원공단</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.ncrc.or.kr/</t>
+          <t>https://www.knps.or.kr/</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1105,23 +1105,23 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>국립공원공단</t>
+          <t>국립광주과학관</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.knps.or.kr/</t>
+          <t>https://www.sciencecenter.or.kr/</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>국립광주과학관</t>
+          <t>국립낙동강생물자원관</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.sciencecenter.or.kr/</t>
+          <t>https://www.nnibr.re.kr/</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>국립낙동강생물자원관</t>
+          <t>국립농업박물관</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.nnibr.re.kr/</t>
+          <t>https://namuk.or.kr/</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>국립농업박물관</t>
+          <t>국립대구과학관</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://namuk.or.kr/</t>
+          <t>https://www.dnsm.or.kr/</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>국립대구과학관</t>
+          <t>국립박물관문화재단</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.dnsm.or.kr/</t>
+          <t>https://www.nmf.or.kr/</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>국립박물관문화재단</t>
+          <t>국립부산과학관</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.nmf.or.kr/</t>
+          <t>http://www.sciport.or.kr/</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1291,17 +1291,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>국립부산과학관</t>
+          <t>국립생태원</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>http://www.sciport.or.kr/</t>
+          <t>http://www.nie.re.kr/</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1311,27 +1311,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>국립생태원</t>
+          <t>국립울진해양과학관</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>http://www.nie.re.kr/</t>
+          <t>https://www.kosm.or.kr/</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1341,17 +1341,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>국립아시아문화전당재단</t>
+          <t>국립중앙의료원</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.accf.or.kr/</t>
+          <t>https://www.nmc.or.kr/</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1381,7 +1381,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>국립울진해양과학관</t>
+          <t>국립항공박물관</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.kosm.or.kr/</t>
+          <t>https://wwww.aviation.or.kr/</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>국립항공박물관</t>
+          <t>국립호남권생물자원관</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://wwww.aviation.or.kr/</t>
+          <t>http://hnibr.re.kr/</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1441,17 +1441,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>국립호남권생물자원관</t>
+          <t>국민건강보험공단</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>http://hnibr.re.kr/</t>
+          <t>https://www.nhis.or.kr/</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1461,27 +1461,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>국민건강보험공단</t>
+          <t>국방과학연구소</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.nhis.or.kr/</t>
+          <t>https://www.add.re.kr/</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1491,17 +1491,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>국방과학연구소</t>
+          <t>국방기술진흥연구소</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.add.re.kr/</t>
+          <t>https://www.krit.re.kr/</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>국방기술진흥연구소</t>
+          <t>국방전직교육원</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.krit.re.kr/</t>
+          <t>https://www.moti.or.kr/</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 실패: 400</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1561,7 +1561,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>국방전직교육원</t>
+          <t>국악방송</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.moti.or.kr/</t>
+          <t>https://www.igbf.kr/</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 400</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>국악방송</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.igbf.kr/</t>
+          <t>https://www.arirang.com/</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>국토교통과학기술진흥원</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.arirang.com/</t>
+          <t>https://www.kaia.re.kr/</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1645,23 +1645,23 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>국토교통과학기술진흥원</t>
+          <t>국토안전관리원</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.kaia.re.kr/</t>
+          <t>http://www.kalis.or.kr/</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1681,17 +1681,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>국토안전관리원</t>
+          <t>그랜드코리아레저(주)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>http://www.kalis.or.kr/</t>
+          <t>https://www.grandkorea.com/</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1705,23 +1705,23 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>그랜드코리아레저(주)</t>
+          <t>근로복지공단</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.grandkorea.com/</t>
+          <t>https://www.comwel.or.kr/</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1731,17 +1731,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: 400</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>근로복지공단</t>
+          <t>기술보증기금</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.comwel.or.kr/</t>
+          <t>https://www.kibo.or.kr/</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 400</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1771,17 +1771,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>기술보증기금</t>
+          <t>농림수산식품교육문화정보원</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.kibo.or.kr/</t>
+          <t>https://www.epis.or.kr/</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1791,27 +1791,27 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>농림수산식품교육문화정보원</t>
+          <t>대한무역투자진흥공사</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.epis.or.kr/</t>
+          <t>http://www.kotra.or.kr/</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1821,27 +1821,27 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
+          <t>대한법률구조공단</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>http://www.kotra.or.kr/</t>
+          <t>https://www.klac.or.kr/</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2031,11 +2031,11 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2311,7 +2311,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>시청자미디어재단</t>
+          <t>식품안전정보원</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.kcmf.or.kr/</t>
+          <t>http://www.foodinfo.or.kr/</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2331,27 +2331,27 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>식품안전정보원</t>
+          <t>신용보증기금</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>http://www.foodinfo.or.kr/</t>
+          <t>http://www.kodit.co.kr/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2365,23 +2365,23 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>신용보증기금</t>
+          <t>신용보증재단중앙회</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>http://www.kodit.co.kr/</t>
+          <t>http://www.koreg.or.kr/</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>신용보증재단중앙회</t>
+          <t>여수광양항만공사</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>http://www.koreg.or.kr/</t>
+          <t>https://www.ygpa.or.kr/</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>양육비이행관리원</t>
+          <t>영상물등급위원회</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.childsupport.or.kr/</t>
+          <t>https://www.kmrb.or.kr/</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2451,17 +2451,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>여수광양항만공사</t>
+          <t>영화진흥위원회</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.ygpa.or.kr/</t>
+          <t>https://www.kofic.or.kr/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>영상물등급위원회</t>
+          <t>오송첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.kmrb.or.kr/</t>
+          <t>https://www.kbiohealth.kr/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>영화진흥위원회</t>
+          <t>육아정책연구소</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.kofic.or.kr/</t>
+          <t>https://www.kicce.re.kr/</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2541,27 +2541,27 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>오송첨단의료산업진흥재단</t>
+          <t>인천국제공항공사</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.kbiohealth.kr/</t>
+          <t>https://www.airport.kr/</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2575,13 +2575,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>육아정책연구소</t>
+          <t>재단법인 건설기술교육원</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.kicce.re.kr/</t>
+          <t>https://www.kicte.or.kr/</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2611,17 +2611,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>인천국제공항공사</t>
+          <t>재단법인 대한건설기계안전관리원</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.airport.kr/</t>
+          <t>https://www.kcesi.or.kr/</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2641,7 +2641,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>재단법인 건설기술교육원</t>
+          <t>재단법인 한국에너지재단</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.kicte.or.kr/</t>
+          <t>https://www.koref.or.kr/</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2671,7 +2671,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>재단법인 대한건설기계안전관리원</t>
+          <t>재외동포협력센터</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.kcesi.or.kr/</t>
+          <t>https://www.okocc.or.kr/</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: 403</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>재단법인 한국에너지재단</t>
+          <t>전국재해구호협회</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.koref.or.kr/</t>
+          <t>https://hopebridge.or.kr/</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2721,27 +2721,27 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>재외동포협력센터</t>
+          <t>정보통신기획평가원</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.okocc.or.kr/</t>
+          <t>http://www.iitp.kr/</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2751,17 +2751,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 403</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>전국재해구호협회</t>
+          <t>정보통신정책연구원</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://hopebridge.or.kr/</t>
+          <t>http://www.kisdi.re.kr/</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>정보통신기획평가원</t>
+          <t>정부법무공단</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>http://www.iitp.kr/</t>
+          <t>http://www.kgls.or.kr/</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2815,23 +2815,23 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>정보통신정책연구원</t>
+          <t>제주국제자유도시개발센터</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>http://www.kisdi.re.kr/</t>
+          <t>https://www.jdcenter.com/</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2845,23 +2845,23 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>정부법무공단</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>http://www.kgls.or.kr/</t>
+          <t>https://www.khug.or.kr/</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2875,23 +2875,23 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>제주국제자유도시개발센터</t>
+          <t>중소벤처기업진흥공단</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.jdcenter.com/</t>
+          <t>https://www.kosmes.or.kr/</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2905,23 +2905,23 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>중앙사회서비스원</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.khug.or.kr/</t>
+          <t>https://www.kcpass.or.kr/</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2935,23 +2935,23 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>중소벤처기업진흥공단</t>
+          <t>충남대학교병원</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.kosmes.or.kr/</t>
+          <t>https://www.cnuh.co.kr/</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>중앙사회서비스원</t>
+          <t>코레일관광개발(주)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.kcpass.or.kr/</t>
+          <t>https://www.korailtravel.com/</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2995,13 +2995,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>충남대학교병원</t>
+          <t>코레일네트웍스(주)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.cnuh.co.kr/</t>
+          <t>https://www.korailnetworks.com/</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>코레일네트웍스(주)</t>
+          <t>코레일테크(주)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.korailnetworks.com/</t>
+          <t>https://www.korailtech.com/</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>코레일테크(주)</t>
+          <t>태권도진흥재단</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.korailtech.com/</t>
+          <t>https://www.tpf.or.kr/</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3081,11 +3081,11 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -3121,17 +3121,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한국고용정보원</t>
+          <t>한국건강증진개발원</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://keis.or.kr/</t>
+          <t>https://www.khepi.or.kr/</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3141,27 +3141,27 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한국과학창의재단</t>
+          <t>한국고용정보원</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.kosac.re.kr/</t>
+          <t>https://keis.or.kr/</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3175,23 +3175,23 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한국광해광업공단</t>
+          <t>한국과학창의재단</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.komir.or.kr/</t>
+          <t>https://www.kosac.re.kr/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3205,23 +3205,23 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한국교육개발원</t>
+          <t>한국광해광업공단</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.kedi.re.kr/</t>
+          <t>https://www.komir.or.kr/</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3231,17 +3231,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한국교육과정평가원</t>
+          <t>한국교육개발원</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.kice.re.kr/</t>
+          <t>https://www.kedi.re.kr/</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3265,13 +3265,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한국교육학술정보원</t>
+          <t>한국교육과정평가원</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.keris.or.kr/</t>
+          <t>https://www.kice.re.kr/</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3295,23 +3295,23 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한국교통안전공단</t>
+          <t>한국교육학술정보원</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.kotsa.or.kr/</t>
+          <t>https://www.keris.or.kr/</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3325,13 +3325,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>한국교통안전공단</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.koica.go.kr/</t>
+          <t>https://www.kotsa.or.kr/</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3361,7 +3361,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한국국토정보공사</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.lx.or.kr/</t>
+          <t>https://www.koica.go.kr/</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3381,27 +3381,27 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한국기상산업기술원</t>
+          <t>한국국토정보공사</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.kmiti.or.kr/</t>
+          <t>https://www.lx.or.kr/</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3415,13 +3415,13 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한국기술교육대학교</t>
+          <t>한국기상산업기술원</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.koreatech.ac.kr/</t>
+          <t>https://www.kmiti.or.kr/</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3445,13 +3445,13 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한국나노기술원</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.kanc.re.kr/</t>
+          <t>https://www.koreatech.ac.kr/</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3481,17 +3481,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한국남동발전(주)</t>
+          <t>한국나노기술원</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.koenergy.kr/</t>
+          <t>https://www.kanc.re.kr/</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한국남부발전(주)</t>
+          <t>한국남동발전(주)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.kospo.co.kr/</t>
+          <t>https://www.koenergy.kr/</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3531,27 +3531,27 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
+          <t>한국남부발전(주)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.at.or.kr/</t>
+          <t>https://www.kospo.co.kr/</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3561,27 +3561,27 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한국농업기술진흥원</t>
+          <t>한국농수산식품유통공사</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.koat.or.kr/</t>
+          <t>https://www.at.or.kr/</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3595,23 +3595,23 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한국도로공사</t>
+          <t>한국농업기술진흥원</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.ex.co.kr/</t>
+          <t>https://www.koat.or.kr/</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3621,27 +3621,27 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국도로공사서비스(주)</t>
+          <t>한국도로공사</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.exservice.co.kr/</t>
+          <t>https://www.ex.co.kr/</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3651,27 +3651,27 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국도로교통공단</t>
+          <t>한국도로공사서비스(주)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.koroad.or.kr/</t>
+          <t>https://www.exservice.co.kr/</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3681,27 +3681,27 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국도박문제예방치유원</t>
+          <t>한국도로교통공단</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.kcgp.or.kr/</t>
+          <t>https://www.koroad.or.kr/</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3721,17 +3721,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국동서발전(주)</t>
+          <t>한국도박문제예방치유원</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.ewp.co.kr/</t>
+          <t>https://www.kcgp.or.kr/</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3751,17 +3751,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국마약퇴치운동본부</t>
+          <t>한국동서발전(주)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://drugfree.or.kr/</t>
+          <t>https://www.ewp.co.kr/</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국문화관광연구원</t>
+          <t>한국마약퇴치운동본부</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>http://www.kcti.re.kr/</t>
+          <t>https://drugfree.or.kr/</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3811,7 +3811,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국물기술인증원</t>
+          <t>한국문화관광연구원</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.kwtc.or.kr/</t>
+          <t>http://www.kcti.re.kr/</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3831,27 +3831,27 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국법무보호복지공단</t>
+          <t>한국물기술인증원</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://koreha.or.kr/</t>
+          <t>https://www.kwtc.or.kr/</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3865,23 +3865,23 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국법제연구원</t>
+          <t>한국법무보호복지공단</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.klri.re.kr/</t>
+          <t>https://koreha.or.kr/</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3901,7 +3901,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>한국법제연구원</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.kvic.or.kr/</t>
+          <t>https://www.klri.re.kr/</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국보건복지인재원</t>
+          <t>한국벤처투자</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.kohi.or.kr/</t>
+          <t>https://www.kvic.or.kr/</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국보건의료연구원</t>
+          <t>한국보건복지인재원</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.neca.re.kr/</t>
+          <t>https://www.kohi.or.kr/</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3981,17 +3981,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국보건의료인국가시험원</t>
+          <t>한국보건의료연구원</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.kuksiwon.or.kr/</t>
+          <t>https://www.neca.re.kr/</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4021,17 +4021,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국부동산원</t>
+          <t>한국보건의료인국가시험원</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.reb.or.kr/</t>
+          <t>https://www.kuksiwon.or.kr/</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4045,23 +4045,23 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국사학진흥재단</t>
+          <t>한국부동산원</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.kasfo.or.kr/</t>
+          <t>https://www.reb.or.kr/</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4075,23 +4075,23 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국사회보장정보원</t>
+          <t>한국사학진흥재단</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>http://www.ssis.or.kr/</t>
+          <t>https://www.kasfo.or.kr/</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4105,23 +4105,23 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국사회복지협의회</t>
+          <t>한국사회보장정보원</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/</t>
+          <t>http://www.ssis.or.kr/</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
+          <t>한국사회복지협의회</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.socialenterprise.or.kr/</t>
+          <t>https://www.bokji.net/</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4161,27 +4161,27 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국산림복지진흥원</t>
+          <t>한국사회적기업진흥원</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://www.fowi.or.kr/</t>
+          <t>https://www.socialenterprise.or.kr/</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4195,23 +4195,23 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한국산업기술시험원</t>
+          <t>한국산림복지진흥원</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.ktl.re.kr/</t>
+          <t>https://www.fowi.or.kr/</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4231,17 +4231,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한국산업기술진흥원</t>
+          <t>한국산업기술시험원</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://www.kiat.or.kr/</t>
+          <t>https://www.ktl.re.kr/</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4255,13 +4255,13 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한국산업단지공단</t>
+          <t>한국산업기술진흥원</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.kicox.or.kr/</t>
+          <t>https://www.kiat.or.kr/</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국산업안전보건공단</t>
+          <t>한국산업단지공단</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://kosha.or.kr/</t>
+          <t>https://www.kicox.or.kr/</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4311,27 +4311,27 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한국산업은행</t>
+          <t>한국산업안전보건공단</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>http://www.kdb.co.kr/</t>
+          <t>https://kosha.or.kr/</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4345,13 +4345,13 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한국생명존중희망재단</t>
+          <t>한국산업은행</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://www.kfsp.or.kr/</t>
+          <t>http://www.kdb.co.kr/</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4375,23 +4375,23 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국서부발전(주)</t>
+          <t>한국생명존중희망재단</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://www.iwest.co.kr/</t>
+          <t>https://www.kfsp.or.kr/</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4405,23 +4405,23 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>한국석유관리원</t>
+          <t>한국서부발전(주)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>http://www.kpetro.or.kr/</t>
+          <t>https://www.iwest.co.kr/</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4435,23 +4435,23 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>한국세라믹기술원</t>
+          <t>한국석유관리원</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://www.kicet.re.kr/</t>
+          <t>http://www.kpetro.or.kr/</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4461,11 +4461,11 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -4681,17 +4681,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국식품산업클러스터진흥원</t>
+          <t>한국승강기안전공단</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://www.foodpolis.kr/</t>
+          <t>https://home.koelsa.or.kr/</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4701,17 +4701,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국식품안전관리인증원</t>
+          <t>한국식품산업클러스터진흥원</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://www.haccp.or.kr/</t>
+          <t>https://www.foodpolis.kr/</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4741,7 +4741,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한국어촌어항공단</t>
+          <t>한국식품안전관리인증원</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://www.fipa.or.kr/</t>
+          <t>https://www.haccp.or.kr/</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한국여성인권진흥원</t>
+          <t>한국양성평등교육진흥원</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://www.stop.or.kr/</t>
+          <t>http://www.kigepe.or.kr/</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한국여성정책연구원</t>
+          <t>한국어촌어항공단</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://www.kwdi.re.kr/</t>
+          <t>https://www.fipa.or.kr/</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4821,27 +4821,27 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>한국원자력환경공단</t>
+          <t>한국여성인권진흥원</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://www.korad.or.kr/</t>
+          <t>https://www.stop.or.kr/</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4861,7 +4861,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>한국의약품안전관리원</t>
+          <t>한국여성정책연구원</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://www.drugsafe.or.kr/</t>
+          <t>https://www.kwdi.re.kr/</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4885,13 +4885,13 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>한국임업진흥원</t>
+          <t>한국예술인복지재단</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://www.kofpi.or.kr/</t>
+          <t>http://www.kawf.kr/</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4911,27 +4911,27 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
+          <t>한국원산지정보원</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>http://www.kamco.or.kr/</t>
+          <t>https://www.origin.or.kr/</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4941,27 +4941,27 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>한국잡월드</t>
+          <t>한국원자력환경공단</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>http://www.koreajobworld.or.kr/</t>
+          <t>https://www.korad.or.kr/</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4981,7 +4981,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>한국장애인개발원</t>
+          <t>한국의약품안전관리원</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://www.koddi.or.kr/</t>
+          <t>https://www.drugsafe.or.kr/</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5005,23 +5005,23 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>한국장학재단</t>
+          <t>한국임업진흥원</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://www.kosaf.go.kr/</t>
+          <t>https://www.kofpi.or.kr/</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5035,23 +5035,23 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>한국재정정보원</t>
+          <t>한국자산관리공사</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://www.fis.kr/</t>
+          <t>http://www.kamco.or.kr/</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5061,27 +5061,27 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>한국전기안전공사</t>
+          <t>한국잡월드</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>http://www.kesco.or.kr/</t>
+          <t>http://www.koreajobworld.or.kr/</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5091,27 +5091,27 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
+          <t>한국장애인개발원</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://kepco.co.kr/</t>
+          <t>https://www.koddi.or.kr/</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5121,27 +5121,27 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
+          <t>한국장학재단</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://www.kepco-enc.com/</t>
+          <t>https://www.kosaf.go.kr/</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5155,23 +5155,23 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>한국조세재정연구원</t>
+          <t>한국재정정보원</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://www.kipf.re.kr/</t>
+          <t>https://www.fis.kr/</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5181,27 +5181,27 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>한국조폐공사</t>
+          <t>한국전기안전공사</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://www.komsco.com/</t>
+          <t>http://www.kesco.or.kr/</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>한국중부발전(주)</t>
+          <t>한국전력공사</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://www.komipo.co.kr/</t>
+          <t>https://kepco.co.kr/</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5241,27 +5241,27 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>한국중소벤처기업유통원</t>
+          <t>한국전력기술주식회사</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://www.kodma.or.kr/</t>
+          <t>https://www.kepco-enc.com/</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5275,23 +5275,23 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>한국지능정보사회진흥원</t>
+          <t>한국조세재정연구원</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://www.nia.or.kr/</t>
+          <t>https://www.kipf.re.kr/</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5311,17 +5311,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>한국지식재산연구원</t>
+          <t>한국조폐공사</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://www.kiip.re.kr/</t>
+          <t>https://www.komsco.com/</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5335,13 +5335,13 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>한국지역난방공사</t>
+          <t>한국중부발전(주)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://www.kdhc.co.kr/</t>
+          <t>https://www.komipo.co.kr/</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5361,17 +5361,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>한국직업능력연구원</t>
+          <t>한국중소벤처기업유통원</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://www.krivet.re.kr/</t>
+          <t>https://www.kodma.or.kr/</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5395,23 +5395,23 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>한국철도공사</t>
+          <t>한국지능정보사회진흥원</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://info.korail.com/</t>
+          <t>https://www.nia.or.kr/</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5425,13 +5425,13 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>한국청소년상담복지개발원</t>
+          <t>한국지식재산연구원</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>http://www.kyci.or.kr/</t>
+          <t>https://www.kiip.re.kr/</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5451,27 +5451,27 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>한국청소년활동진흥원</t>
+          <t>한국지역난방공사</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://www.kywa.or.kr/</t>
+          <t>https://www.kdhc.co.kr/</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5491,7 +5491,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>한국치산기술협회</t>
+          <t>한국직업능력연구원</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://www.kafet.or.kr/</t>
+          <t>https://www.krivet.re.kr/</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5511,27 +5511,27 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>한국투자공사</t>
+          <t>한국철도공사</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://www.kic.kr/</t>
+          <t>https://info.korail.com/</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5545,13 +5545,13 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>한국특허정보원</t>
+          <t>한국청소년상담복지개발원</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://www.kipi.or.kr/</t>
+          <t>http://www.kyci.or.kr/</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>한국항로표지기술원</t>
+          <t>한국치산기술협회</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://www.katon.or.kr/</t>
+          <t>https://www.kafet.or.kr/</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5601,27 +5601,27 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>한국해양교통안전공단</t>
+          <t>한국투자공사</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://www.komsa.or.kr/</t>
+          <t>https://www.kic.kr/</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>한국해양수산개발원</t>
+          <t>한국특허정보원</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://www.kmi.re.kr/</t>
+          <t>https://www.kipi.or.kr/</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>한국해양조사협회</t>
+          <t>한국항로표지기술원</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://www.khra.kr/</t>
+          <t>https://www.katon.or.kr/</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5701,17 +5701,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>한국해양진흥공사</t>
+          <t>한국해양교통안전공단</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://www.kobc.or.kr/</t>
+          <t>https://www.komsa.or.kr/</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5721,17 +5721,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
+          <t>한국해양수산개발원</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://www.keci.or.kr/</t>
+          <t>https://www.kmi.re.kr/</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5761,17 +5761,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>한전KPS(주)</t>
+          <t>한국해양조사협회</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://www.kps.co.kr/</t>
+          <t>https://www.khra.kr/</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5791,7 +5791,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>항공안전기술원</t>
+          <t>한국해양진흥공사</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://www.kiast.or.kr/</t>
+          <t>https://www.kobc.or.kr/</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>해양수산과학기술진흥원</t>
+          <t>한국환경보전원</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://www.kimst.re.kr/</t>
+          <t>https://www.keci.or.kr/</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -5851,30 +5851,120 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
+          <t>한전KPS(주)</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://www.kps.co.kr/</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>항공안전기술원</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://www.kiast.or.kr/</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>해양수산과학기술진흥원</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://www.kimst.re.kr/</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
           <t>해양환경공단</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>https://www.koem.or.kr/</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>유효 게시판 없음</t>
-        </is>
-      </c>
-      <c r="F182" t="n">
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>유효 게시판 없음</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
         <v>1</v>
       </c>
     </row>

--- a/boards_missing.xlsx
+++ b/boards_missing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(재)일제강제동원피해자지원재단</t>
+          <t>(재)축산환경관리원</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.fomo.or.kr/</t>
+          <t>https://www.lemi.or.kr/</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -561,17 +561,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(재)축산환경관리원</t>
+          <t>(재)한국통계정보원</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.lemi.or.kr/</t>
+          <t>https://www.kosii.or.kr/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>(재)한국통계정보원</t>
+          <t>(주)공영홈쇼핑</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.kosii.or.kr/</t>
+          <t>https://www.gongyoung.kr/</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -631,17 +631,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(주)공영홈쇼핑</t>
+          <t>(주)한국가스기술공사</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.gongyoung.kr/</t>
+          <t>https://www.kogas-tech.or.kr/</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -651,27 +651,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: 403</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(주)한국가스기술공사</t>
+          <t>88관광개발(주)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.kogas-tech.or.kr/</t>
+          <t>https://www.88countryclub.co.kr/</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -681,17 +681,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 403</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>88관광개발(주)</t>
+          <t>가축위생방역지원본부</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.88countryclub.co.kr/</t>
+          <t>https://www.lhca.or.kr/</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>가축위생방역지원본부</t>
+          <t>강원대학교병원</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.lhca.or.kr/</t>
+          <t>https://www.knuh.or.kr/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -751,17 +751,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>강원대학교병원</t>
+          <t>건강보험심사평가원</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.knuh.or.kr/</t>
+          <t>https://www.hira.or.kr/</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -781,17 +781,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>건강보험심사평가원</t>
+          <t>경상국립대학교병원</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.hira.or.kr/</t>
+          <t>http://www.gnuh.co.kr/</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>경상국립대학교병원</t>
+          <t>공간정보산업진흥원</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>http://www.gnuh.co.kr/</t>
+          <t>https://www.spacen.or.kr/</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -831,17 +831,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>공간정보산업진흥원</t>
+          <t>과학기술사업화진흥원</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.spacen.or.kr/</t>
+          <t>https://www.compa.re.kr/</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -861,17 +861,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>공간정보품질관리원</t>
+          <t>과학기술정책연구원</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.siqms.or.kr/</t>
+          <t>https://www.stepi.re.kr/</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -891,27 +891,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>공무원연금공단</t>
+          <t>국가수리과학연구소</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.geps.or.kr/</t>
+          <t>http://www.nims.re.kr/</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -921,17 +921,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>과학기술사업화진흥원</t>
+          <t>국가아동권리보장원</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.compa.re.kr/</t>
+          <t>https://www.ncrc.or.kr/</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -955,23 +955,23 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>과학기술정책연구원</t>
+          <t>국가철도공단</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.stepi.re.kr/</t>
+          <t>https://www.kr.or.kr/</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -981,27 +981,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>국가수리과학연구소</t>
+          <t>국립공원공단</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>http://www.nims.re.kr/</t>
+          <t>https://www.knps.or.kr/</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>국가아동권리보장원</t>
+          <t>국립광주과학관</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.ncrc.or.kr/</t>
+          <t>https://www.sciencecenter.or.kr/</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1041,27 +1041,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>국가철도공단</t>
+          <t>국립농업박물관</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.kr.or.kr/</t>
+          <t>https://namuk.or.kr/</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1071,27 +1071,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>국립공원공단</t>
+          <t>국립대구과학관</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.knps.or.kr/</t>
+          <t>https://www.dnsm.or.kr/</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>국립광주과학관</t>
+          <t>국립박물관문화재단</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.sciencecenter.or.kr/</t>
+          <t>https://www.nmf.or.kr/</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>국립낙동강생물자원관</t>
+          <t>국립부산과학관</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.nnibr.re.kr/</t>
+          <t>http://www.sciport.or.kr/</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1161,27 +1161,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>국립농업박물관</t>
+          <t>국립생태원</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://namuk.or.kr/</t>
+          <t>http://www.nie.re.kr/</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>국립대구과학관</t>
+          <t>국립울진해양과학관</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.dnsm.or.kr/</t>
+          <t>https://www.kosm.or.kr/</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>국립박물관문화재단</t>
+          <t>국립항공박물관</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.nmf.or.kr/</t>
+          <t>https://wwww.aviation.or.kr/</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>국립부산과학관</t>
+          <t>국민건강보험공단</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>http://www.sciport.or.kr/</t>
+          <t>https://www.nhis.or.kr/</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1291,17 +1291,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>국립생태원</t>
+          <t>국방과학연구소</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>http://www.nie.re.kr/</t>
+          <t>https://www.add.re.kr/</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>국립울진해양과학관</t>
+          <t>국방기술진흥연구소</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.kosm.or.kr/</t>
+          <t>https://www.krit.re.kr/</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1341,17 +1341,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>국립중앙의료원</t>
+          <t>국방전직교육원</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.nmc.or.kr/</t>
+          <t>https://www.moti.or.kr/</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 실패: 400</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1381,7 +1381,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>국립항공박물관</t>
+          <t>국악방송</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://wwww.aviation.or.kr/</t>
+          <t>https://www.igbf.kr/</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>국립호남권생물자원관</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>http://hnibr.re.kr/</t>
+          <t>https://www.arirang.com/</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>국민건강보험공단</t>
+          <t>국토교통과학기술진흥원</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.nhis.or.kr/</t>
+          <t>https://www.kaia.re.kr/</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1471,17 +1471,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>국방과학연구소</t>
+          <t>국토안전관리원</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.add.re.kr/</t>
+          <t>http://www.kalis.or.kr/</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1495,23 +1495,23 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>국방기술진흥연구소</t>
+          <t>그랜드코리아레저(주)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.krit.re.kr/</t>
+          <t>https://www.grandkorea.com/</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1521,27 +1521,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>국방전직교육원</t>
+          <t>근로복지공단</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.moti.or.kr/</t>
+          <t>https://www.comwel.or.kr/</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1561,17 +1561,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>국악방송</t>
+          <t>기술보증기금</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.igbf.kr/</t>
+          <t>https://www.kibo.or.kr/</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>농림수산식품교육문화정보원</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.arirang.com/</t>
+          <t>https://www.epis.or.kr/</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>국토교통과학기술진흥원</t>
+          <t>대외경제정책연구원</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.kaia.re.kr/</t>
+          <t>https://www.kiep.go.kr/</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1651,17 +1651,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>국토안전관리원</t>
+          <t>대한법률구조공단</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>http://www.kalis.or.kr/</t>
+          <t>https://www.klac.or.kr/</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1671,27 +1671,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>그랜드코리아레저(주)</t>
+          <t>대한석탄공사</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.grandkorea.com/</t>
+          <t>https://www.kocoal.or.kr/</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>근로복지공단</t>
+          <t>대한장애인체육회</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.comwel.or.kr/</t>
+          <t>http://www.koreanpc.kr/</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 400</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1741,17 +1741,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>기술보증기금</t>
+          <t>대한체육회</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.kibo.or.kr/</t>
+          <t>https://www.sports.or.kr/</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1761,17 +1761,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>농림수산식품교육문화정보원</t>
+          <t>동남권원자력의학원</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.epis.or.kr/</t>
+          <t>https://www.dirams.re.kr/</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1795,23 +1795,23 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>대한무역투자진흥공사</t>
+          <t>무역안보관리원</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>http://www.kotra.or.kr/</t>
+          <t>https://www.kosti.or.kr/</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>대한법률구조공단</t>
+          <t>민주화운동기념사업회</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.klac.or.kr/</t>
+          <t>https://www.kdemo.or.kr/</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>대한석탄공사</t>
+          <t>부산대학교병원</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.kocoal.or.kr/</t>
+          <t>http://www.pnuh.or.kr/</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>대한장애인체육회</t>
+          <t>부산대학교치과병원</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>http://www.koreanpc.kr/</t>
+          <t>https://www.pnudh.co.kr/</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1921,7 +1921,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>대한체육회</t>
+          <t>북한이탈주민지원재단</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.sports.or.kr/</t>
+          <t>https://www.koreahana.or.kr/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>독립기념관</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.i815.or.kr/</t>
+          <t>https://www.tp.or.kr/</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>동남권원자력의학원</t>
+          <t>서민금융진흥원</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.dirams.re.kr/</t>
+          <t>https://www.kinfa.or.kr/</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2005,13 +2005,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>민주화운동기념사업회</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.kdemo.or.kr/</t>
+          <t>http://snuh.org/</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2031,17 +2031,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>부산대학교병원</t>
+          <t>선박해양플랜트연구소</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>http://www.pnuh.or.kr/</t>
+          <t>https://www.kriso.re.kr/</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2071,17 +2071,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>부산대학교치과병원</t>
+          <t>소상공인시장진흥공단</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.pnudh.co.kr/</t>
+          <t>https://www.semas.or.kr/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2091,17 +2091,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>북한이탈주민지원재단</t>
+          <t>수도권매립지관리공사</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.koreahana.or.kr/</t>
+          <t>http://www.slc.or.kr/</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>시청자미디어재단</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.tp.or.kr/</t>
+          <t>https://www.kcmf.or.kr/</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>서민금융진흥원</t>
+          <t>식품안전정보원</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.kinfa.or.kr/</t>
+          <t>http://www.foodinfo.or.kr/</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2191,17 +2191,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>서울대학교병원</t>
+          <t>신용보증기금</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>http://snuh.org/</t>
+          <t>http://www.kodit.co.kr/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>선박해양플랜트연구소</t>
+          <t>신용보증재단중앙회</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.kriso.re.kr/</t>
+          <t>http://www.koreg.or.kr/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2245,23 +2245,23 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>소상공인시장진흥공단</t>
+          <t>여수광양항만공사</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.semas.or.kr/</t>
+          <t>https://www.ygpa.or.kr/</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>수도권매립지관리공사</t>
+          <t>영상물등급위원회</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>http://www.slc.or.kr/</t>
+          <t>https://www.kmrb.or.kr/</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>식품안전정보원</t>
+          <t>영화진흥위원회</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>http://www.foodinfo.or.kr/</t>
+          <t>https://www.kofic.or.kr/</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2331,27 +2331,27 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>신용보증기금</t>
+          <t>오송첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>http://www.kodit.co.kr/</t>
+          <t>https://www.kbiohealth.kr/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2371,7 +2371,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>신용보증재단중앙회</t>
+          <t>육아정책연구소</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>http://www.koreg.or.kr/</t>
+          <t>https://www.kicce.re.kr/</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2401,17 +2401,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>여수광양항만공사</t>
+          <t>인천국제공항공사</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.ygpa.or.kr/</t>
+          <t>https://www.airport.kr/</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2425,13 +2425,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>영상물등급위원회</t>
+          <t>재단법인 건설기술교육원</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.kmrb.or.kr/</t>
+          <t>https://www.kicte.or.kr/</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>영화진흥위원회</t>
+          <t>재단법인 대한건설기계안전관리원</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.kofic.or.kr/</t>
+          <t>https://www.kcesi.or.kr/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>오송첨단의료산업진흥재단</t>
+          <t>재단법인 한국에너지재단</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.kbiohealth.kr/</t>
+          <t>https://www.koref.or.kr/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>육아정책연구소</t>
+          <t>재외동포협력센터</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.kicce.re.kr/</t>
+          <t>https://www.okocc.or.kr/</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2541,27 +2541,27 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: 403</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>인천국제공항공사</t>
+          <t>전국재해구호협회</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.airport.kr/</t>
+          <t>https://hopebridge.or.kr/</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2571,27 +2571,27 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>재단법인 건설기술교육원</t>
+          <t>정보통신기획평가원</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.kicte.or.kr/</t>
+          <t>http://www.iitp.kr/</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>재단법인 대한건설기계안전관리원</t>
+          <t>정보통신정책연구원</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.kcesi.or.kr/</t>
+          <t>http://www.kisdi.re.kr/</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2631,17 +2631,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>재단법인 한국에너지재단</t>
+          <t>정부법무공단</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.koref.or.kr/</t>
+          <t>http://www.kgls.or.kr/</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2665,23 +2665,23 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>재외동포협력센터</t>
+          <t>제주국제자유도시개발센터</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.okocc.or.kr/</t>
+          <t>https://www.jdcenter.com/</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2691,27 +2691,27 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: 403</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>전국재해구호협회</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://hopebridge.or.kr/</t>
+          <t>https://www.khug.or.kr/</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2721,27 +2721,27 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>정보통신기획평가원</t>
+          <t>중소벤처기업진흥공단</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>http://www.iitp.kr/</t>
+          <t>https://www.kosmes.or.kr/</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>정보통신정책연구원</t>
+          <t>중앙사회서비스원</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>http://www.kisdi.re.kr/</t>
+          <t>https://www.kcpass.or.kr/</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2785,13 +2785,13 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>정부법무공단</t>
+          <t>충남대학교병원</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>http://www.kgls.or.kr/</t>
+          <t>https://www.cnuh.co.kr/</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2815,23 +2815,23 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>제주국제자유도시개발센터</t>
+          <t>코레일관광개발(주)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.jdcenter.com/</t>
+          <t>https://www.korailtravel.com/</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2845,23 +2845,23 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>코레일네트웍스(주)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.khug.or.kr/</t>
+          <t>https://www.korailnetworks.com/</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2871,27 +2871,27 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>중소벤처기업진흥공단</t>
+          <t>코레일테크(주)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.kosmes.or.kr/</t>
+          <t>https://www.korailtech.com/</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2911,7 +2911,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>중앙사회서비스원</t>
+          <t>학교법인한국폴리텍</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.kcpass.or.kr/</t>
+          <t>http://www.kopo.ac.kr/</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>충남대학교병원</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.cnuh.co.kr/</t>
+          <t>https://www.kogas.or.kr/</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2965,23 +2965,23 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>코레일관광개발(주)</t>
+          <t>한국고용정보원</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.korailtravel.com/</t>
+          <t>https://keis.or.kr/</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>코레일네트웍스(주)</t>
+          <t>한국과학창의재단</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.korailnetworks.com/</t>
+          <t>https://www.kosac.re.kr/</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3021,27 +3021,27 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>코레일테크(주)</t>
+          <t>한국광해광업공단</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.korailtech.com/</t>
+          <t>https://www.komir.or.kr/</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3055,13 +3055,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>태권도진흥재단</t>
+          <t>한국교육개발원</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.tpf.or.kr/</t>
+          <t>https://www.kedi.re.kr/</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3081,27 +3081,27 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>한국교육과정평가원</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.kogas.or.kr/</t>
+          <t>https://www.kice.re.kr/</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>한국건강증진개발원</t>
+          <t>한국교육학술정보원</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.khepi.or.kr/</t>
+          <t>https://www.keris.or.kr/</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3141,17 +3141,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>한국고용정보원</t>
+          <t>한국교통안전공단</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://keis.or.kr/</t>
+          <t>https://www.kotsa.or.kr/</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3175,23 +3175,23 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>한국과학창의재단</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.kosac.re.kr/</t>
+          <t>https://www.koica.go.kr/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3201,27 +3201,27 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>한국광해광업공단</t>
+          <t>한국국토정보공사</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.komir.or.kr/</t>
+          <t>https://www.lx.or.kr/</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3231,17 +3231,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>한국교육개발원</t>
+          <t>한국기상산업기술원</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.kedi.re.kr/</t>
+          <t>https://www.kmiti.or.kr/</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3271,7 +3271,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>한국교육과정평가원</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.kice.re.kr/</t>
+          <t>https://www.koreatech.ac.kr/</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3301,7 +3301,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>한국교육학술정보원</t>
+          <t>한국나노기술원</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.keris.or.kr/</t>
+          <t>https://www.kanc.re.kr/</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3325,23 +3325,23 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>한국교통안전공단</t>
+          <t>한국남동발전(주)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.kotsa.or.kr/</t>
+          <t>https://www.koenergy.kr/</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3355,23 +3355,23 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>한국국제협력단</t>
+          <t>한국남부발전(주)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.koica.go.kr/</t>
+          <t>https://www.kospo.co.kr/</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3391,7 +3391,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>한국국토정보공사</t>
+          <t>한국농수산식품유통공사</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.lx.or.kr/</t>
+          <t>https://www.at.or.kr/</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>한국기상산업기술원</t>
+          <t>한국농업기술진흥원</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.kmiti.or.kr/</t>
+          <t>https://www.koat.or.kr/</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3451,17 +3451,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>한국기술교육대학교</t>
+          <t>한국도로공사</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.koreatech.ac.kr/</t>
+          <t>https://www.ex.co.kr/</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3471,17 +3471,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>한국나노기술원</t>
+          <t>한국도로공사서비스(주)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.kanc.re.kr/</t>
+          <t>https://www.exservice.co.kr/</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3505,23 +3505,23 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>한국남동발전(주)</t>
+          <t>한국도로교통공단</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.koenergy.kr/</t>
+          <t>https://www.koroad.or.kr/</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3531,27 +3531,27 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>한국남부발전(주)</t>
+          <t>한국도박문제예방치유원</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.kospo.co.kr/</t>
+          <t>https://www.kcgp.or.kr/</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3571,17 +3571,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
+          <t>한국동서발전(주)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.at.or.kr/</t>
+          <t>https://www.ewp.co.kr/</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한국농업기술진흥원</t>
+          <t>한국마약퇴치운동본부</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.koat.or.kr/</t>
+          <t>https://drugfree.or.kr/</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3621,27 +3621,27 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국도로공사</t>
+          <t>한국문화관광연구원</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.ex.co.kr/</t>
+          <t>http://www.kcti.re.kr/</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3661,7 +3661,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국도로공사서비스(주)</t>
+          <t>한국물기술인증원</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.exservice.co.kr/</t>
+          <t>https://www.kwtc.or.kr/</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3685,13 +3685,13 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국도로교통공단</t>
+          <t>한국법무보호복지공단</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.koroad.or.kr/</t>
+          <t>https://koreha.or.kr/</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국도박문제예방치유원</t>
+          <t>한국법제연구원</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.kcgp.or.kr/</t>
+          <t>https://www.klri.re.kr/</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3745,23 +3745,23 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국동서발전(주)</t>
+          <t>한국벤처투자</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.ewp.co.kr/</t>
+          <t>https://www.kvic.or.kr/</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3775,13 +3775,13 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국마약퇴치운동본부</t>
+          <t>한국보건의료연구원</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://drugfree.or.kr/</t>
+          <t>https://www.neca.re.kr/</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3811,7 +3811,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국문화관광연구원</t>
+          <t>한국보건의료인국가시험원</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>http://www.kcti.re.kr/</t>
+          <t>https://www.kuksiwon.or.kr/</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3841,17 +3841,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국물기술인증원</t>
+          <t>한국부동산원</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.kwtc.or.kr/</t>
+          <t>https://www.reb.or.kr/</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3865,23 +3865,23 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국법무보호복지공단</t>
+          <t>한국사학진흥재단</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://koreha.or.kr/</t>
+          <t>https://www.kasfo.or.kr/</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3895,23 +3895,23 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국법제연구원</t>
+          <t>한국사회보장정보원</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.klri.re.kr/</t>
+          <t>http://www.ssis.or.kr/</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>한국사회복지협의회</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.kvic.or.kr/</t>
+          <t>https://www.bokji.net/</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국보건복지인재원</t>
+          <t>한국사회적기업진흥원</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.kohi.or.kr/</t>
+          <t>https://www.socialenterprise.or.kr/</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3985,23 +3985,23 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국보건의료연구원</t>
+          <t>한국산림복지진흥원</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.neca.re.kr/</t>
+          <t>https://www.fowi.or.kr/</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4021,7 +4021,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국보건의료인국가시험원</t>
+          <t>한국산업기술시험원</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.kuksiwon.or.kr/</t>
+          <t>https://www.ktl.re.kr/</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4045,23 +4045,23 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국부동산원</t>
+          <t>한국산업기술진흥원</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.reb.or.kr/</t>
+          <t>https://www.kiat.or.kr/</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4075,23 +4075,23 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국사학진흥재단</t>
+          <t>한국산업단지공단</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.kasfo.or.kr/</t>
+          <t>https://www.kicox.or.kr/</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4101,17 +4101,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국사회보장정보원</t>
+          <t>한국산업안전보건공단</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>http://www.ssis.or.kr/</t>
+          <t>https://kosha.or.kr/</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4135,13 +4135,13 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한국사회복지협의회</t>
+          <t>한국산업은행</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/</t>
+          <t>http://www.kdb.co.kr/</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4161,17 +4161,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국사회적기업진흥원</t>
+          <t>한국생명존중희망재단</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://www.socialenterprise.or.kr/</t>
+          <t>https://www.kfsp.or.kr/</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4195,23 +4195,23 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한국산림복지진흥원</t>
+          <t>한국서부발전(주)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://www.fowi.or.kr/</t>
+          <t>https://www.iwest.co.kr/</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4225,23 +4225,23 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한국산업기술시험원</t>
+          <t>한국석유관리원</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://www.ktl.re.kr/</t>
+          <t>http://www.kpetro.or.kr/</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4261,17 +4261,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한국산업기술진흥원</t>
+          <t>한국소방산업기술원</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://www.kiat.or.kr/</t>
+          <t>https://www.kfi.or.kr/</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientResponseError</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국산업단지공단</t>
+          <t>한국소비자원</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://www.kicox.or.kr/</t>
+          <t>https://www.kca.go.kr/</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4311,27 +4311,27 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한국산업안전보건공단</t>
+          <t>한국수력원자력(주)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://kosha.or.kr/</t>
+          <t>https://www.khnp.co.kr/</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4351,17 +4351,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한국산업은행</t>
+          <t>한국수목원정원관리원</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>http://www.kdb.co.kr/</t>
+          <t>https://www.koagi.or.kr/</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4381,17 +4381,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국생명존중희망재단</t>
+          <t>한국수자원공사</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://www.kfsp.or.kr/</t>
+          <t>https://www.kwater.or.kr/</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4405,23 +4405,23 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>한국서부발전(주)</t>
+          <t>한국수출입은행</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://www.iwest.co.kr/</t>
+          <t>https://www.koreaexim.go.kr/</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4431,27 +4431,27 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>한국석유관리원</t>
+          <t>한국식품산업클러스터진흥원</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>http://www.kpetro.or.kr/</t>
+          <t>https://www.foodpolis.kr/</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>한국소방산업기술원</t>
+          <t>한국식품안전관리인증원</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://www.kfi.or.kr/</t>
+          <t>https://www.haccp.or.kr/</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4491,27 +4491,27 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientResponseError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>한국소비자원</t>
+          <t>한국어촌어항공단</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.kca.go.kr/</t>
+          <t>https://www.fipa.or.kr/</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4521,27 +4521,27 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>한국수력원자력(주)</t>
+          <t>한국여성인권진흥원</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://www.khnp.co.kr/</t>
+          <t>https://www.stop.or.kr/</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4555,23 +4555,23 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>한국수목원정원관리원</t>
+          <t>한국여성정책연구원</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://www.koagi.or.kr/</t>
+          <t>https://www.kwdi.re.kr/</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4591,17 +4591,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>한국수자원공사</t>
+          <t>한국원자력환경공단</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://www.kwater.or.kr/</t>
+          <t>https://www.korad.or.kr/</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4615,13 +4615,13 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>한국수출입은행</t>
+          <t>한국의약품안전관리원</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://www.koreaexim.go.kr/</t>
+          <t>https://www.drugsafe.or.kr/</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>한국스포츠레저(주)</t>
+          <t>한국임업진흥원</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://www.kospole.co.kr/</t>
+          <t>https://www.kofpi.or.kr/</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4671,27 +4671,27 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>한국승강기안전공단</t>
+          <t>한국자산관리공사</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>준정부기관(기금관리형)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://home.koelsa.or.kr/</t>
+          <t>http://www.kamco.or.kr/</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4701,17 +4701,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국식품산업클러스터진흥원</t>
+          <t>한국잡월드</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://www.foodpolis.kr/</t>
+          <t>http://www.koreajobworld.or.kr/</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4731,17 +4731,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한국식품안전관리인증원</t>
+          <t>한국장애인개발원</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://www.haccp.or.kr/</t>
+          <t>https://www.koddi.or.kr/</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4771,17 +4771,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한국양성평등교육진흥원</t>
+          <t>한국장학재단</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>http://www.kigepe.or.kr/</t>
+          <t>https://www.kosaf.go.kr/</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4791,27 +4791,27 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한국어촌어항공단</t>
+          <t>한국재정정보원</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://www.fipa.or.kr/</t>
+          <t>https://www.fis.kr/</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4821,27 +4821,27 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>한국여성인권진흥원</t>
+          <t>한국전기안전공사</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://www.stop.or.kr/</t>
+          <t>http://www.kesco.or.kr/</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4861,17 +4861,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>한국여성정책연구원</t>
+          <t>한국전력공사</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://www.kwdi.re.kr/</t>
+          <t>https://kepco.co.kr/</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4881,27 +4881,27 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>한국예술인복지재단</t>
+          <t>한국전력기술주식회사</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>http://www.kawf.kr/</t>
+          <t>https://www.kepco-enc.com/</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4911,17 +4911,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>한국원산지정보원</t>
+          <t>한국조세재정연구원</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://www.origin.or.kr/</t>
+          <t>https://www.kipf.re.kr/</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4941,27 +4941,27 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>한국원자력환경공단</t>
+          <t>한국조폐공사</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://www.korad.or.kr/</t>
+          <t>https://www.komsco.com/</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4975,23 +4975,23 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>한국의약품안전관리원</t>
+          <t>한국중부발전(주)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://www.drugsafe.or.kr/</t>
+          <t>https://www.komipo.co.kr/</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5005,13 +5005,13 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>한국임업진흥원</t>
+          <t>한국중소벤처기업유통원</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://www.kofpi.or.kr/</t>
+          <t>https://www.kodma.or.kr/</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5041,17 +5041,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
+          <t>한국지능정보사회진흥원</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>준정부기관(기금관리형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>http://www.kamco.or.kr/</t>
+          <t>https://www.nia.or.kr/</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5065,13 +5065,13 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>한국잡월드</t>
+          <t>한국지식재산연구원</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>http://www.koreajobworld.or.kr/</t>
+          <t>https://www.kiip.re.kr/</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5091,27 +5091,27 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>한국장애인개발원</t>
+          <t>한국지역난방공사</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(시장형)</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://www.koddi.or.kr/</t>
+          <t>https://www.kdhc.co.kr/</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5121,27 +5121,27 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>한국장학재단</t>
+          <t>한국직업능력연구원</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://www.kosaf.go.kr/</t>
+          <t>https://www.krivet.re.kr/</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5161,17 +5161,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>한국재정정보원</t>
+          <t>한국철도공사</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://www.fis.kr/</t>
+          <t>https://info.korail.com/</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5181,27 +5181,27 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>한국전기안전공사</t>
+          <t>한국청소년상담복지개발원</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>http://www.kesco.or.kr/</t>
+          <t>http://www.kyci.or.kr/</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5211,27 +5211,27 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 시간 초과</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
+          <t>한국출판문화산업진흥원</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://kepco.co.kr/</t>
+          <t>http://www.kpipa.or.kr/</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -5251,17 +5251,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
+          <t>한국치산기술협회</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://www.kepco-enc.com/</t>
+          <t>https://www.kafet.or.kr/</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5271,17 +5271,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>유효 게시판 없음</t>
+          <t>홈페이지 접속 실패: ClientConnectorError</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>한국조세재정연구원</t>
+          <t>한국투자공사</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://www.kipf.re.kr/</t>
+          <t>https://www.kic.kr/</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5305,23 +5305,23 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>한국조폐공사</t>
+          <t>한국특허정보원</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://www.komsco.com/</t>
+          <t>https://www.kipi.or.kr/</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5335,23 +5335,23 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>한국중부발전(주)</t>
+          <t>한국해양교통안전공단</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://www.komipo.co.kr/</t>
+          <t>https://www.komsa.or.kr/</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5371,7 +5371,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>한국중소벤처기업유통원</t>
+          <t>한국해양수산개발원</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://www.kodma.or.kr/</t>
+          <t>https://www.kmi.re.kr/</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5401,17 +5401,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>한국지능정보사회진흥원</t>
+          <t>한국해양조사협회</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://www.nia.or.kr/</t>
+          <t>https://www.khra.kr/</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5431,7 +5431,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>한국지식재산연구원</t>
+          <t>한국해양진흥공사</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://www.kiip.re.kr/</t>
+          <t>https://www.kobc.or.kr/</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5455,23 +5455,23 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>한국지역난방공사</t>
+          <t>한국환경보전원</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>공기업(시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://www.kdhc.co.kr/</t>
+          <t>https://www.keci.or.kr/</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5491,17 +5491,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>한국직업능력연구원</t>
+          <t>한전KPS(주)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://www.krivet.re.kr/</t>
+          <t>https://www.kps.co.kr/</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5515,23 +5515,23 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>한국철도공사</t>
+          <t>항공안전기술원</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://info.korail.com/</t>
+          <t>https://www.kiast.or.kr/</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5545,13 +5545,13 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>한국청소년상담복지개발원</t>
+          <t>해양수산과학기술진흥원</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>http://www.kyci.or.kr/</t>
+          <t>https://www.kimst.re.kr/</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>홈페이지 접속 시간 초과</t>
+          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5581,17 +5581,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>한국치산기술협회</t>
+          <t>해양환경공단</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>공기업(준시장형)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://www.kafet.or.kr/</t>
+          <t>https://www.koem.or.kr/</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5601,370 +5601,10 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>홈페이지 접속 실패: ClientConnectorError</t>
+          <t>유효 게시판 없음</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>한국투자공사</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>https://www.kic.kr/</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>유효 게시판 없음</t>
-        </is>
-      </c>
-      <c r="F174" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>한국특허정보원</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>https://www.kipi.or.kr/</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>유효 게시판 없음</t>
-        </is>
-      </c>
-      <c r="F175" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>한국항로표지기술원</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>https://www.katon.or.kr/</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>유효 게시판 없음</t>
-        </is>
-      </c>
-      <c r="F176" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>한국해양교통안전공단</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>준정부기관(위탁집행형)</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>https://www.komsa.or.kr/</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>홈페이지 접속 시간 초과</t>
-        </is>
-      </c>
-      <c r="F177" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>한국해양수산개발원</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>https://www.kmi.re.kr/</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>유효 게시판 없음</t>
-        </is>
-      </c>
-      <c r="F178" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>한국해양조사협회</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>https://www.khra.kr/</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>유효 게시판 없음</t>
-        </is>
-      </c>
-      <c r="F179" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>한국해양진흥공사</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>https://www.kobc.or.kr/</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>유효 게시판 없음</t>
-        </is>
-      </c>
-      <c r="F180" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>한국환경보전원</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>https://www.keci.or.kr/</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>홈페이지 접속 실패: ClientConnectorDNSError</t>
-        </is>
-      </c>
-      <c r="F181" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>한전KPS(주)</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>공기업(준시장형)</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>https://www.kps.co.kr/</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>유효 게시판 없음</t>
-        </is>
-      </c>
-      <c r="F182" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>항공안전기술원</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>https://www.kiast.or.kr/</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>유효 게시판 없음</t>
-        </is>
-      </c>
-      <c r="F183" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>해양수산과학기술진흥원</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>https://www.kimst.re.kr/</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>홈페이지 접속 실패: ClientConnectorSSLError</t>
-        </is>
-      </c>
-      <c r="F184" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>해양환경공단</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>공기업(준시장형)</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>https://www.koem.or.kr/</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>유효 게시판 없음</t>
-        </is>
-      </c>
-      <c r="F185" t="n">
         <v>1</v>
       </c>
     </row>
